--- a/dados/SURVEY_VESSELS/SURVEY_VESSELS.xlsx
+++ b/dados/SURVEY_VESSELS/SURVEY_VESSELS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/SURVEY_VESSELS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\projetos\ofi\dados\SURVEY_VESSELS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="958" documentId="8_{2FDA8D28-226B-473E-B58F-AB3C8EEAFC38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C627920-AEE1-495C-88D9-3E79E98964C8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF39B58F-8543-431A-B145-91B012CDC963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="3" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="66">
   <si>
     <t>cbo</t>
   </si>
@@ -237,6 +237,9 @@
   </si>
   <si>
     <t>status</t>
+  </si>
+  <si>
+    <t>embarcacao</t>
   </si>
 </sst>
 </file>
@@ -639,15 +642,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{490C43E3-ED93-4C78-B9B5-276EDD51C5AB}">
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -661,7 +664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -675,7 +678,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -689,7 +692,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -703,7 +706,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -717,7 +720,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -731,7 +734,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>57</v>
       </c>
@@ -745,7 +748,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -759,7 +762,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -773,7 +776,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -787,7 +790,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -801,7 +804,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -815,7 +818,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -829,7 +832,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -843,7 +846,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -857,7 +860,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -868,7 +871,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -879,7 +882,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -890,7 +893,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -898,7 +901,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -906,17 +909,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -929,21 +932,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DC0AFA-9444-4F11-ABC1-7475EEC3A448}">
   <dimension ref="A1:O27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" customWidth="1"/>
-    <col min="8" max="8" width="23.28515625" customWidth="1"/>
+    <col min="1" max="2" width="16.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
+    <col min="8" max="8" width="23.33203125" customWidth="1"/>
     <col min="11" max="11" width="21" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="14.109375" customWidth="1"/>
+    <col min="14" max="14" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
         <v>58</v>
@@ -967,7 +970,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -979,7 +982,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -991,7 +994,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1003,7 +1006,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1015,7 +1018,7 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -1027,7 +1030,7 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -1039,7 +1042,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>57</v>
       </c>
@@ -1051,7 +1054,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -1063,7 +1066,7 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -1075,7 +1078,7 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1087,7 +1090,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1099,7 +1102,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -1111,7 +1114,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1123,7 +1126,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -1135,7 +1138,7 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1147,7 +1150,7 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -1159,7 +1162,7 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1171,7 +1174,7 @@
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1183,7 +1186,7 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -1195,7 +1198,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -1207,7 +1210,7 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1220,7 +1223,7 @@
       <c r="J22" s="1"/>
       <c r="O22" s="4"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -1232,10 +1235,10 @@
       <c r="H23" s="1"/>
       <c r="J23" s="1"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J24" s="1"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -1244,7 +1247,7 @@
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -1253,7 +1256,7 @@
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J27" s="1"/>
     </row>
   </sheetData>
@@ -1267,22 +1270,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00B80E83-9236-40C9-95ED-72F039A44EB0}">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="8" max="8" width="24.140625" customWidth="1"/>
-    <col min="9" max="9" width="20.28515625" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" customWidth="1"/>
+    <col min="9" max="9" width="20.33203125" customWidth="1"/>
+    <col min="11" max="11" width="15.6640625" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
         <v>58</v>
@@ -1306,7 +1309,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="20.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1317,7 +1320,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -1328,7 +1331,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1339,7 +1342,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1350,7 +1353,7 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -1361,7 +1364,7 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1372,7 +1375,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1383,7 +1386,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -1394,7 +1397,7 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -1405,7 +1408,7 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -1416,7 +1419,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -1428,7 +1431,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1440,7 +1443,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -1452,7 +1455,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1464,19 +1467,19 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="18" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="10:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J22" s="1"/>
     </row>
   </sheetData>
@@ -1488,23 +1491,23 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC0244D8-3EC3-425D-A328-9D6A0DAB3C45}">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.42578125" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" style="5" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="22.28515625" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" customWidth="1"/>
+    <col min="9" max="9" width="23.109375" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>58</v>
@@ -1528,7 +1531,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -1540,7 +1543,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -1552,7 +1555,7 @@
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1564,7 +1567,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -1576,7 +1579,7 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -1588,7 +1591,7 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -1600,7 +1603,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -1610,7 +1613,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -1622,7 +1625,7 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1634,7 +1637,7 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>56</v>
       </c>
@@ -1646,7 +1649,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1659,7 +1662,7 @@
       <c r="I12" s="1"/>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1671,7 +1674,7 @@
       <c r="I13" s="1"/>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1682,7 +1685,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1693,7 +1696,7 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1704,7 +1707,7 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1715,7 +1718,7 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
